--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2000</f>
+              <f>'Time Series'!$A$2:$A$2001</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2000</f>
+              <f>'Time Series'!$B$2:$B$2001</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2000</f>
+              <f>'Time Series'!$A$2:$A$2001</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2000</f>
+              <f>'Time Series'!$C$2:$C$2001</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2000</f>
+              <f>'Time Series'!$A$2:$A$2001</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2000</f>
+              <f>'Time Series'!$E$2:$E$2001</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-12 12:00</t>
+          <t>Last Updated: 2026-09-13 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,887</t>
+          <t>25,876</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.43%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,782</t>
+          <t>25,822</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,796</t>
+          <t>25,837</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.43%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2000"/>
+  <dimension ref="A1:O2001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40095,6 +40095,40 @@
       </c>
       <c r="M2000" t="n">
         <v>25917</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B2001" t="n">
+        <v>25876.38</v>
+      </c>
+      <c r="C2001" t="n">
+        <v>25765</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>-111.380000000001</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>-0.4304311499521997</v>
+      </c>
+      <c r="G2001" t="n">
+        <v>25750</v>
+      </c>
+      <c r="H2001" t="n">
+        <v>25780</v>
+      </c>
+      <c r="K2001" t="n">
+        <v>25822</v>
+      </c>
+      <c r="L2001" t="n">
+        <v>25837</v>
+      </c>
+      <c r="M2001" t="n">
+        <v>25915</v>
       </c>
     </row>
   </sheetData>
@@ -40856,13 +40890,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25966</v>
+        <v>25959</v>
       </c>
       <c r="C68" t="n">
-        <v>25781</v>
+        <v>25780</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.71</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40970,12 +41004,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,782</t>
+          <t>25,822</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,796</t>
+          <t>25,837</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -40988,12 +41022,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,917</t>
+          <t>25,915</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,917</t>
+          <t>25,915</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2001</f>
+              <f>'Time Series'!$A$2:$A$2002</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2001</f>
+              <f>'Time Series'!$B$2:$B$2002</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2001</f>
+              <f>'Time Series'!$A$2:$A$2002</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2001</f>
+              <f>'Time Series'!$C$2:$C$2002</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2001</f>
+              <f>'Time Series'!$A$2:$A$2002</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2001</f>
+              <f>'Time Series'!$E$2:$E$2002</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-13 12:00</t>
+          <t>Last Updated: 2026-09-14 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,876</t>
+          <t>25,873</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,765</t>
+          <t>25,785</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.34%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,811</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,837</t>
+          <t>25,816</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.34%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.66%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2001"/>
+  <dimension ref="A1:O2002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40129,6 +40129,40 @@
       </c>
       <c r="M2001" t="n">
         <v>25915</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2002" t="n">
+        <v>25872.72</v>
+      </c>
+      <c r="C2002" t="n">
+        <v>25785</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>-87.72000000000116</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>-0.3390443679675008</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>25760</v>
+      </c>
+      <c r="H2002" t="n">
+        <v>25810</v>
+      </c>
+      <c r="K2002" t="n">
+        <v>25811</v>
+      </c>
+      <c r="L2002" t="n">
+        <v>25816</v>
+      </c>
+      <c r="M2002" t="n">
+        <v>25979</v>
       </c>
     </row>
   </sheetData>
@@ -40890,13 +40924,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25959</v>
+        <v>25953</v>
       </c>
       <c r="C68" t="n">
         <v>25780</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -40950,12 +40984,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,750</t>
+          <t>25,760</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,780</t>
+          <t>25,810</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -40986,12 +41020,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,970</t>
+          <t>25,984</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25,870</t>
+          <t>25,884</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41004,12 +41038,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,811</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,837</t>
+          <t>25,816</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41022,12 +41056,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,915</t>
+          <t>25,979</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,915</t>
+          <t>25,979</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2002</f>
+              <f>'Time Series'!$A$2:$A$2003</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2002</f>
+              <f>'Time Series'!$B$2:$B$2003</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2002</f>
+              <f>'Time Series'!$A$2:$A$2003</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2002</f>
+              <f>'Time Series'!$C$2:$C$2003</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2002</f>
+              <f>'Time Series'!$A$2:$A$2003</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2002</f>
+              <f>'Time Series'!$E$2:$E$2003</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-14 12:00</t>
+          <t>Last Updated: 2026-09-15 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,873</t>
+          <t>25,928</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,785</t>
+          <t>25,745</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.70%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,811</t>
+          <t>25,740</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,816</t>
+          <t>25,751</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.70%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.67%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2002"/>
+  <dimension ref="A1:O2003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40163,6 +40163,40 @@
       </c>
       <c r="M2002" t="n">
         <v>25979</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2003" t="n">
+        <v>25927.6</v>
+      </c>
+      <c r="C2003" t="n">
+        <v>25745</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>-182.5999999999985</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>-0.7042688100711155</v>
+      </c>
+      <c r="G2003" t="n">
+        <v>25720</v>
+      </c>
+      <c r="H2003" t="n">
+        <v>25770</v>
+      </c>
+      <c r="K2003" t="n">
+        <v>25740</v>
+      </c>
+      <c r="L2003" t="n">
+        <v>25751</v>
+      </c>
+      <c r="M2003" t="n">
+        <v>25956</v>
       </c>
     </row>
   </sheetData>
@@ -40924,10 +40958,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25953</v>
+        <v>25951</v>
       </c>
       <c r="C68" t="n">
-        <v>25780</v>
+        <v>25778</v>
       </c>
       <c r="D68" t="n">
         <v>-0.67</v>
@@ -40984,12 +41018,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,760</t>
+          <t>25,720</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,810</t>
+          <t>25,770</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41020,12 +41054,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,984</t>
+          <t>26,028</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25,884</t>
+          <t>25,928</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41038,12 +41072,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,811</t>
+          <t>25,740</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,816</t>
+          <t>25,751</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41056,12 +41090,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,979</t>
+          <t>25,956</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,979</t>
+          <t>25,956</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2003</f>
+              <f>'Time Series'!$A$2:$A$2004</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2003</f>
+              <f>'Time Series'!$B$2:$B$2004</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2003</f>
+              <f>'Time Series'!$A$2:$A$2004</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2003</f>
+              <f>'Time Series'!$C$2:$C$2004</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2003</f>
+              <f>'Time Series'!$A$2:$A$2004</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2003</f>
+              <f>'Time Series'!$E$2:$E$2004</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-15 12:00</t>
+          <t>Last Updated: 2026-09-16 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,928</t>
+          <t>25,904</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>-0.61%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,740</t>
+          <t>25,782</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,751</t>
+          <t>25,802</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>-0.61%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2003"/>
+  <dimension ref="A1:O2004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40197,6 +40197,40 @@
       </c>
       <c r="M2003" t="n">
         <v>25956</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2004" t="n">
+        <v>25904.22</v>
+      </c>
+      <c r="C2004" t="n">
+        <v>25745</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>-159.2200000000012</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>-0.6146488873241547</v>
+      </c>
+      <c r="G2004" t="n">
+        <v>25720</v>
+      </c>
+      <c r="H2004" t="n">
+        <v>25770</v>
+      </c>
+      <c r="K2004" t="n">
+        <v>25782</v>
+      </c>
+      <c r="L2004" t="n">
+        <v>25802</v>
+      </c>
+      <c r="M2004" t="n">
+        <v>25982</v>
       </c>
     </row>
   </sheetData>
@@ -40958,10 +40992,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25951</v>
+        <v>25949</v>
       </c>
       <c r="C68" t="n">
-        <v>25778</v>
+        <v>25776</v>
       </c>
       <c r="D68" t="n">
         <v>-0.67</v>
@@ -41054,12 +41088,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,028</t>
+          <t>25,887</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25,928</t>
+          <t>25,987</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41072,12 +41106,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,740</t>
+          <t>25,782</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,751</t>
+          <t>25,802</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41090,12 +41124,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,956</t>
+          <t>25,982</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,956</t>
+          <t>25,982</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2004</f>
+              <f>'Time Series'!$A$2:$A$2005</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2004</f>
+              <f>'Time Series'!$B$2:$B$2005</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2004</f>
+              <f>'Time Series'!$A$2:$A$2005</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2004</f>
+              <f>'Time Series'!$C$2:$C$2005</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2004</f>
+              <f>'Time Series'!$A$2:$A$2005</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2004</f>
+              <f>'Time Series'!$E$2:$E$2005</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-16 12:00</t>
+          <t>Last Updated: 2026-09-17 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,904</t>
+          <t>25,960</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,745</t>
+          <t>25,795</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-0.64%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,782</t>
+          <t>25,908</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,802</t>
+          <t>25,919</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-0.64%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.64%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2004"/>
+  <dimension ref="A1:O2005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40231,6 +40231,40 @@
       </c>
       <c r="M2004" t="n">
         <v>25982</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2005" t="n">
+        <v>25960.35</v>
+      </c>
+      <c r="C2005" t="n">
+        <v>25795</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>-165.3499999999985</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>-0.6369328610746717</v>
+      </c>
+      <c r="G2005" t="n">
+        <v>25770</v>
+      </c>
+      <c r="H2005" t="n">
+        <v>25820</v>
+      </c>
+      <c r="K2005" t="n">
+        <v>25908</v>
+      </c>
+      <c r="L2005" t="n">
+        <v>25919</v>
+      </c>
+      <c r="M2005" t="n">
+        <v>25989</v>
       </c>
     </row>
   </sheetData>
@@ -40995,10 +41029,10 @@
         <v>25949</v>
       </c>
       <c r="C68" t="n">
-        <v>25776</v>
+        <v>25777</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -41052,12 +41086,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,720</t>
+          <t>25,770</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,770</t>
+          <t>25,820</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41088,12 +41122,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,887</t>
+          <t>25,904</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25,987</t>
+          <t>26,004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41106,12 +41140,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,782</t>
+          <t>25,908</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,802</t>
+          <t>25,919</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41124,12 +41158,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,982</t>
+          <t>25,989</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,982</t>
+          <t>25,989</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2005</f>
+              <f>'Time Series'!$A$2:$A$2006</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2005</f>
+              <f>'Time Series'!$B$2:$B$2006</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2005</f>
+              <f>'Time Series'!$A$2:$A$2006</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2005</f>
+              <f>'Time Series'!$C$2:$C$2006</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2005</f>
+              <f>'Time Series'!$A$2:$A$2006</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2005</f>
+              <f>'Time Series'!$E$2:$E$2006</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-17 12:00</t>
+          <t>Last Updated: 2026-09-18 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,960</t>
+          <t>25,964</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,795</t>
+          <t>25,855</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.42%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,908</t>
+          <t>25,878</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,919</t>
+          <t>25,890</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.42%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.61%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2005"/>
+  <dimension ref="A1:O2006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40265,6 +40265,40 @@
       </c>
       <c r="M2005" t="n">
         <v>25989</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2006" t="n">
+        <v>25964.16</v>
+      </c>
+      <c r="C2006" t="n">
+        <v>25855</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>-109.1599999999999</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>-0.4204256944957967</v>
+      </c>
+      <c r="G2006" t="n">
+        <v>25830</v>
+      </c>
+      <c r="H2006" t="n">
+        <v>25880</v>
+      </c>
+      <c r="K2006" t="n">
+        <v>25878</v>
+      </c>
+      <c r="L2006" t="n">
+        <v>25890</v>
+      </c>
+      <c r="M2006" t="n">
+        <v>26002</v>
       </c>
     </row>
   </sheetData>
@@ -41026,13 +41060,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25949</v>
+        <v>25950</v>
       </c>
       <c r="C68" t="n">
-        <v>25777</v>
+        <v>25781</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -41086,12 +41120,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,770</t>
+          <t>25,830</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,820</t>
+          <t>25,880</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41122,12 +41156,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,904</t>
+          <t>25,917</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,004</t>
+          <t>26,017</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41140,12 +41174,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,908</t>
+          <t>25,878</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,919</t>
+          <t>25,890</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41158,12 +41192,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,989</t>
+          <t>26,002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,989</t>
+          <t>26,002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2006</f>
+              <f>'Time Series'!$A$2:$A$2007</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2006</f>
+              <f>'Time Series'!$B$2:$B$2007</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2006</f>
+              <f>'Time Series'!$A$2:$A$2007</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2006</f>
+              <f>'Time Series'!$C$2:$C$2007</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2006</f>
+              <f>'Time Series'!$A$2:$A$2007</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2006</f>
+              <f>'Time Series'!$E$2:$E$2007</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-18 12:00</t>
+          <t>Last Updated: 2026-09-19 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,964</t>
+          <t>26,002</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,855</t>
+          <t>25,905</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.37%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,878</t>
+          <t>25,910</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,890</t>
+          <t>25,920</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.37%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-0.59%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2006"/>
+  <dimension ref="A1:O2007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40299,6 +40299,40 @@
       </c>
       <c r="M2006" t="n">
         <v>26002</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2007" t="n">
+        <v>26002.27</v>
+      </c>
+      <c r="C2007" t="n">
+        <v>25905</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>-97.27000000000044</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>-0.3740827243159941</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>25890</v>
+      </c>
+      <c r="H2007" t="n">
+        <v>25920</v>
+      </c>
+      <c r="K2007" t="n">
+        <v>25910</v>
+      </c>
+      <c r="L2007" t="n">
+        <v>25920</v>
+      </c>
+      <c r="M2007" t="n">
+        <v>26015</v>
       </c>
     </row>
   </sheetData>
@@ -41060,13 +41094,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25950</v>
+        <v>25953</v>
       </c>
       <c r="C68" t="n">
-        <v>25781</v>
+        <v>25788</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -41120,12 +41154,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,830</t>
+          <t>25,890</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,880</t>
+          <t>25,920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41156,12 +41190,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,917</t>
+          <t>25,914</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,017</t>
+          <t>26,014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41174,12 +41208,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,878</t>
+          <t>25,910</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,890</t>
+          <t>25,920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41192,12 +41226,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,002</t>
+          <t>26,015</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26,002</t>
+          <t>26,015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2007</f>
+              <f>'Time Series'!$A$2:$A$2008</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2007</f>
+              <f>'Time Series'!$B$2:$B$2008</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2007</f>
+              <f>'Time Series'!$A$2:$A$2008</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2007</f>
+              <f>'Time Series'!$C$2:$C$2008</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2007</f>
+              <f>'Time Series'!$A$2:$A$2008</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2007</f>
+              <f>'Time Series'!$E$2:$E$2008</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-19 12:00</t>
+          <t>Last Updated: 2026-09-20 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,002</t>
+          <t>26,128</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.85%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,910</t>
+          <t>25,917</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>25,934</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.85%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.60%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2007"/>
+  <dimension ref="A1:O2008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40333,6 +40333,40 @@
       </c>
       <c r="M2007" t="n">
         <v>26015</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B2008" t="n">
+        <v>26127.62</v>
+      </c>
+      <c r="C2008" t="n">
+        <v>25905</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>-222.619999999999</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>-0.8520485218324478</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>25890</v>
+      </c>
+      <c r="H2008" t="n">
+        <v>25920</v>
+      </c>
+      <c r="K2008" t="n">
+        <v>25917</v>
+      </c>
+      <c r="L2008" t="n">
+        <v>25934</v>
+      </c>
+      <c r="M2008" t="n">
+        <v>26011</v>
       </c>
     </row>
   </sheetData>
@@ -41094,13 +41128,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25953</v>
+        <v>25962</v>
       </c>
       <c r="C68" t="n">
-        <v>25788</v>
+        <v>25794</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -41208,12 +41242,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,910</t>
+          <t>25,917</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>25,934</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41226,12 +41260,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,015</t>
+          <t>26,011</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26,015</t>
+          <t>26,011</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2008</f>
+              <f>'Time Series'!$A$2:$A$2009</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2008</f>
+              <f>'Time Series'!$B$2:$B$2009</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2008</f>
+              <f>'Time Series'!$A$2:$A$2009</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2008</f>
+              <f>'Time Series'!$C$2:$C$2009</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2008</f>
+              <f>'Time Series'!$A$2:$A$2009</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2008</f>
+              <f>'Time Series'!$E$2:$E$2009</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-20 12:00</t>
+          <t>Last Updated: 2026-09-21 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,128</t>
+          <t>25,995</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,905</t>
+          <t>25,950</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-0.17%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,917</t>
+          <t>25,886</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,934</t>
+          <t>25,902</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-0.17%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2008"/>
+  <dimension ref="A1:O2009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40367,6 +40367,40 @@
       </c>
       <c r="M2008" t="n">
         <v>26011</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2009" t="n">
+        <v>25994.94</v>
+      </c>
+      <c r="C2009" t="n">
+        <v>25950</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>-44.93999999999869</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>-0.1728797989147068</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>25900</v>
+      </c>
+      <c r="H2009" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K2009" t="n">
+        <v>25886</v>
+      </c>
+      <c r="L2009" t="n">
+        <v>25902</v>
+      </c>
+      <c r="M2009" t="n">
+        <v>26017</v>
       </c>
     </row>
   </sheetData>
@@ -41128,13 +41162,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25962</v>
+        <v>25963</v>
       </c>
       <c r="C68" t="n">
-        <v>25794</v>
+        <v>25801</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
@@ -41188,12 +41222,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,890</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41224,12 +41258,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,914</t>
+          <t>25,948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,014</t>
+          <t>26,048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41242,12 +41276,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,917</t>
+          <t>25,886</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,934</t>
+          <t>25,902</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41260,12 +41294,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,011</t>
+          <t>26,017</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26,011</t>
+          <t>26,017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2009</f>
+              <f>'Time Series'!$A$2:$A$2010</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2009</f>
+              <f>'Time Series'!$B$2:$B$2010</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2009</f>
+              <f>'Time Series'!$A$2:$A$2010</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2009</f>
+              <f>'Time Series'!$C$2:$C$2010</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2009</f>
+              <f>'Time Series'!$A$2:$A$2010</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2009</f>
+              <f>'Time Series'!$E$2:$E$2010</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-21 12:00</t>
+          <t>Last Updated: 2026-09-22 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,995</t>
+          <t>25,970</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,950</t>
+          <t>25,895</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.29%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,886</t>
+          <t>25,876</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,902</t>
+          <t>25,888</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.29%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2009"/>
+  <dimension ref="A1:O2010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40401,6 +40401,40 @@
       </c>
       <c r="M2009" t="n">
         <v>26017</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2010" t="n">
+        <v>25969.65</v>
+      </c>
+      <c r="C2010" t="n">
+        <v>25895</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>-74.65000000000146</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>-0.2874509282951501</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>25870</v>
+      </c>
+      <c r="H2010" t="n">
+        <v>25920</v>
+      </c>
+      <c r="K2010" t="n">
+        <v>25876</v>
+      </c>
+      <c r="L2010" t="n">
+        <v>25888</v>
+      </c>
+      <c r="M2010" t="n">
+        <v>26006</v>
       </c>
     </row>
   </sheetData>
@@ -41165,10 +41199,10 @@
         <v>25963</v>
       </c>
       <c r="C68" t="n">
-        <v>25801</v>
+        <v>25805</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -41222,12 +41256,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>25,870</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>25,920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41258,12 +41292,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,948</t>
+          <t>25,951</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,048</t>
+          <t>26,051</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41276,12 +41310,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,886</t>
+          <t>25,876</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,902</t>
+          <t>25,888</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41294,12 +41328,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,017</t>
+          <t>26,006</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26,017</t>
+          <t>26,006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2010</f>
+              <f>'Time Series'!$A$2:$A$2011</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2010</f>
+              <f>'Time Series'!$B$2:$B$2011</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2010</f>
+              <f>'Time Series'!$A$2:$A$2011</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2010</f>
+              <f>'Time Series'!$C$2:$C$2011</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2010</f>
+              <f>'Time Series'!$A$2:$A$2011</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2010</f>
+              <f>'Time Series'!$E$2:$E$2011</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-22 12:00</t>
+          <t>Last Updated: 2026-09-23 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,970</t>
+          <t>25,972</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,895</t>
+          <t>25,825</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.56%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,876</t>
+          <t>25,892</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,888</t>
+          <t>25,905</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.56%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2010"/>
+  <dimension ref="A1:O2011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40435,6 +40435,40 @@
       </c>
       <c r="M2010" t="n">
         <v>26006</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2011" t="n">
+        <v>25971.63</v>
+      </c>
+      <c r="C2011" t="n">
+        <v>25825</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>-146.630000000001</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>-0.564577579458821</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>25800</v>
+      </c>
+      <c r="H2011" t="n">
+        <v>25850</v>
+      </c>
+      <c r="K2011" t="n">
+        <v>25892</v>
+      </c>
+      <c r="L2011" t="n">
+        <v>25905</v>
+      </c>
+      <c r="M2011" t="n">
+        <v>26005</v>
       </c>
     </row>
   </sheetData>
@@ -41196,10 +41230,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25963</v>
+        <v>25964</v>
       </c>
       <c r="C68" t="n">
-        <v>25805</v>
+        <v>25806</v>
       </c>
       <c r="D68" t="n">
         <v>-0.61</v>
@@ -41256,12 +41290,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,870</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>25,850</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41292,12 +41326,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,951</t>
+          <t>25,947</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,051</t>
+          <t>26,047</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41310,12 +41344,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,876</t>
+          <t>25,892</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,888</t>
+          <t>25,905</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41328,12 +41362,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,006</t>
+          <t>26,005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26,006</t>
+          <t>26,005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2011</f>
+              <f>'Time Series'!$A$2:$A$2012</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2011</f>
+              <f>'Time Series'!$B$2:$B$2012</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2011</f>
+              <f>'Time Series'!$A$2:$A$2012</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2011</f>
+              <f>'Time Series'!$C$2:$C$2012</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2011</f>
+              <f>'Time Series'!$A$2:$A$2012</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2011</f>
+              <f>'Time Series'!$E$2:$E$2012</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-23 12:00</t>
+          <t>Last Updated: 2026-09-24 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,972</t>
+          <t>25,962</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.53%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,892</t>
+          <t>25,931</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,905</t>
+          <t>25,940</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.53%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2011"/>
+  <dimension ref="A1:O2012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40469,6 +40469,40 @@
       </c>
       <c r="M2011" t="n">
         <v>26005</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2012" t="n">
+        <v>25961.69</v>
+      </c>
+      <c r="C2012" t="n">
+        <v>25825</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>-136.6899999999987</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>-0.5265065563913547</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>25800</v>
+      </c>
+      <c r="H2012" t="n">
+        <v>25850</v>
+      </c>
+      <c r="K2012" t="n">
+        <v>25931</v>
+      </c>
+      <c r="L2012" t="n">
+        <v>25940</v>
+      </c>
+      <c r="M2012" t="n">
+        <v>25983</v>
       </c>
     </row>
   </sheetData>
@@ -41233,10 +41267,10 @@
         <v>25964</v>
       </c>
       <c r="C68" t="n">
-        <v>25806</v>
+        <v>25807</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.61</v>
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -41326,12 +41360,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,947</t>
+          <t>25,948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,047</t>
+          <t>26,048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41344,12 +41378,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,892</t>
+          <t>25,931</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,905</t>
+          <t>25,940</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41362,12 +41396,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,005</t>
+          <t>25,983</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26,005</t>
+          <t>25,983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2012</f>
+              <f>'Time Series'!$A$2:$A$2013</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2012</f>
+              <f>'Time Series'!$B$2:$B$2013</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2012</f>
+              <f>'Time Series'!$A$2:$A$2013</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2012</f>
+              <f>'Time Series'!$C$2:$C$2013</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2012</f>
+              <f>'Time Series'!$A$2:$A$2013</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2012</f>
+              <f>'Time Series'!$E$2:$E$2013</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-24 12:00</t>
+          <t>Last Updated: 2026-09-25 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,962</t>
+          <t>25,951</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,825</t>
+          <t>25,910</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.16%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,931</t>
+          <t>25,966</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>25,988</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.16%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.58%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2012"/>
+  <dimension ref="A1:O2013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40503,6 +40503,40 @@
       </c>
       <c r="M2012" t="n">
         <v>25983</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2013" t="n">
+        <v>25950.54</v>
+      </c>
+      <c r="C2013" t="n">
+        <v>25910</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>-40.54000000000087</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>-0.1562202559176066</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>25890</v>
+      </c>
+      <c r="H2013" t="n">
+        <v>25930</v>
+      </c>
+      <c r="K2013" t="n">
+        <v>25966</v>
+      </c>
+      <c r="L2013" t="n">
+        <v>25988</v>
+      </c>
+      <c r="M2013" t="n">
+        <v>25971</v>
       </c>
     </row>
   </sheetData>
@@ -41264,13 +41298,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25964</v>
+        <v>25963</v>
       </c>
       <c r="C68" t="n">
-        <v>25807</v>
+        <v>25811</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -41324,12 +41358,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>25,890</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,850</t>
+          <t>25,930</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41360,12 +41394,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,948</t>
+          <t>25,947</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,048</t>
+          <t>26,047</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41378,12 +41412,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,931</t>
+          <t>25,966</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>25,988</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41396,12 +41430,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,983</t>
+          <t>25,971</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,983</t>
+          <t>25,971</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2013</f>
+              <f>'Time Series'!$A$2:$A$2014</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2013</f>
+              <f>'Time Series'!$B$2:$B$2014</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2013</f>
+              <f>'Time Series'!$A$2:$A$2014</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2013</f>
+              <f>'Time Series'!$C$2:$C$2014</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2013</f>
+              <f>'Time Series'!$A$2:$A$2014</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2013</f>
+              <f>'Time Series'!$E$2:$E$2014</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-25 12:00</t>
+          <t>Last Updated: 2026-09-26 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,951</t>
+          <t>25,966</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,910</t>
+          <t>25,975</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,966</t>
+          <t>26,004</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,988</t>
+          <t>26,013</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-0.55%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2013"/>
+  <dimension ref="A1:O2014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40536,6 +40536,40 @@
         <v>25988</v>
       </c>
       <c r="M2013" t="n">
+        <v>25971</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2014" t="n">
+        <v>25965.7</v>
+      </c>
+      <c r="C2014" t="n">
+        <v>25975</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>9.299999999999272</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>0.03581648097297309</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>25950</v>
+      </c>
+      <c r="H2014" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K2014" t="n">
+        <v>26004</v>
+      </c>
+      <c r="L2014" t="n">
+        <v>26013</v>
+      </c>
+      <c r="M2014" t="n">
         <v>25971</v>
       </c>
     </row>
@@ -41301,10 +41335,10 @@
         <v>25963</v>
       </c>
       <c r="C68" t="n">
-        <v>25811</v>
+        <v>25817</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -41358,12 +41392,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,890</t>
+          <t>25,950</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,930</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41394,12 +41428,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,947</t>
+          <t>25,935</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,047</t>
+          <t>26,035</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41412,12 +41446,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,966</t>
+          <t>26,004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,988</t>
+          <t>26,013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2014</f>
+              <f>'Time Series'!$A$2:$A$2015</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2014</f>
+              <f>'Time Series'!$B$2:$B$2015</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2014</f>
+              <f>'Time Series'!$A$2:$A$2015</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2014</f>
+              <f>'Time Series'!$C$2:$C$2015</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2014</f>
+              <f>'Time Series'!$A$2:$A$2015</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2014</f>
+              <f>'Time Series'!$E$2:$E$2015</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-26 12:00</t>
+          <t>Last Updated: 2026-09-27 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,966</t>
+          <t>25,952</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,004</t>
+          <t>25,986</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,013</t>
+          <t>25,998</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-0.53%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2014"/>
+  <dimension ref="A1:O2015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40570,6 +40570,40 @@
         <v>26013</v>
       </c>
       <c r="M2014" t="n">
+        <v>25971</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B2015" t="n">
+        <v>25952.11</v>
+      </c>
+      <c r="C2015" t="n">
+        <v>25975</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>22.88999999999942</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>0.08820092084997874</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>25950</v>
+      </c>
+      <c r="H2015" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K2015" t="n">
+        <v>25986</v>
+      </c>
+      <c r="L2015" t="n">
+        <v>25998</v>
+      </c>
+      <c r="M2015" t="n">
         <v>25971</v>
       </c>
     </row>
@@ -41335,10 +41369,10 @@
         <v>25963</v>
       </c>
       <c r="C68" t="n">
-        <v>25817</v>
+        <v>25823</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -41446,12 +41480,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,004</t>
+          <t>25,986</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,013</t>
+          <t>25,998</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2015</f>
+              <f>'Time Series'!$A$2:$A$2016</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2015</f>
+              <f>'Time Series'!$B$2:$B$2016</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2015</f>
+              <f>'Time Series'!$A$2:$A$2016</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2015</f>
+              <f>'Time Series'!$C$2:$C$2016</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2015</f>
+              <f>'Time Series'!$A$2:$A$2016</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2015</f>
+              <f>'Time Series'!$E$2:$E$2016</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-27 12:00</t>
+          <t>Last Updated: 2026-09-28 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,952</t>
+          <t>25,937</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,975</t>
+          <t>25,925</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,986</t>
+          <t>26,019</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,998</t>
+          <t>26,025</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.50%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2015"/>
+  <dimension ref="A1:O2016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40605,6 +40605,40 @@
       </c>
       <c r="M2015" t="n">
         <v>25971</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B2016" t="n">
+        <v>25936.55</v>
+      </c>
+      <c r="C2016" t="n">
+        <v>25925</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>-11.54999999999927</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>-0.04453175152439038</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>25900</v>
+      </c>
+      <c r="H2016" t="n">
+        <v>25950</v>
+      </c>
+      <c r="K2016" t="n">
+        <v>26019</v>
+      </c>
+      <c r="L2016" t="n">
+        <v>26025</v>
+      </c>
+      <c r="M2016" t="n">
+        <v>25963</v>
       </c>
     </row>
   </sheetData>
@@ -41366,13 +41400,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25963</v>
+        <v>25962</v>
       </c>
       <c r="C68" t="n">
-        <v>25823</v>
+        <v>25827</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.54</v>
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -41426,12 +41460,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>25,900</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>25,950</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>26,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41462,12 +41496,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,935</t>
+          <t>25,963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,035</t>
+          <t>26,083</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41480,12 +41514,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,986</t>
+          <t>26,019</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,998</t>
+          <t>26,025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41498,12 +41532,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,971</t>
+          <t>25,963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,971</t>
+          <t>25,963</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2016</f>
+              <f>'Time Series'!$A$2:$A$2017</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2016</f>
+              <f>'Time Series'!$B$2:$B$2017</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2016</f>
+              <f>'Time Series'!$A$2:$A$2017</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2016</f>
+              <f>'Time Series'!$C$2:$C$2017</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2016</f>
+              <f>'Time Series'!$A$2:$A$2017</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2016</f>
+              <f>'Time Series'!$E$2:$E$2017</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-28 12:00</t>
+          <t>Last Updated: 2026-09-29 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,937</t>
+          <t>25,917</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,019</t>
+          <t>26,062</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,025</t>
+          <t>26,070</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-0.49%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2016"/>
+  <dimension ref="A1:O2017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40639,6 +40639,37 @@
       </c>
       <c r="M2016" t="n">
         <v>25963</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2017" t="n">
+        <v>25917.43</v>
+      </c>
+      <c r="C2017" t="n">
+        <v>25925</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>7.569999999999709</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>0.02920814293701076</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>25900</v>
+      </c>
+      <c r="H2017" t="n">
+        <v>25950</v>
+      </c>
+      <c r="K2017" t="n">
+        <v>26062</v>
+      </c>
+      <c r="L2017" t="n">
+        <v>26070</v>
       </c>
     </row>
   </sheetData>
@@ -41400,13 +41431,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25962</v>
+        <v>25960</v>
       </c>
       <c r="C68" t="n">
-        <v>25827</v>
+        <v>25830</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -41496,12 +41527,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,963</t>
+          <t>25,933</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,083</t>
+          <t>26,033</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41514,12 +41545,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,019</t>
+          <t>26,062</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,025</t>
+          <t>26,070</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41532,12 +41563,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,963</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,963</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2017</f>
+              <f>'Time Series'!$A$2:$A$2018</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2017</f>
+              <f>'Time Series'!$B$2:$B$2018</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2017</f>
+              <f>'Time Series'!$A$2:$A$2018</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2017</f>
+              <f>'Time Series'!$C$2:$C$2018</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2017</f>
+              <f>'Time Series'!$A$2:$A$2018</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2017</f>
+              <f>'Time Series'!$E$2:$E$2018</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-29 12:00</t>
+          <t>Last Updated: 2026-09-30 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,917</t>
+          <t>25,933</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,062</t>
+          <t>26,004</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,070</t>
+          <t>26,014</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.11%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2017"/>
+  <dimension ref="A1:O2018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40670,6 +40670,40 @@
       </c>
       <c r="L2017" t="n">
         <v>26070</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2018" t="n">
+        <v>25933.06</v>
+      </c>
+      <c r="C2018" t="n">
+        <v>25925</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>-8.06000000000131</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>-0.03108001909532199</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>25900</v>
+      </c>
+      <c r="H2018" t="n">
+        <v>25950</v>
+      </c>
+      <c r="K2018" t="n">
+        <v>26004</v>
+      </c>
+      <c r="L2018" t="n">
+        <v>26014</v>
+      </c>
+      <c r="M2018" t="n">
+        <v>25955</v>
       </c>
     </row>
   </sheetData>
@@ -41431,13 +41465,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25960</v>
+        <v>25959</v>
       </c>
       <c r="C68" t="n">
-        <v>25830</v>
+        <v>25833</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -41545,12 +41579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,062</t>
+          <t>26,004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,070</t>
+          <t>26,014</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41563,12 +41597,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>25,955</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>25,955</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2018</f>
+              <f>'Time Series'!$A$2:$A$2019</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2018</f>
+              <f>'Time Series'!$B$2:$B$2019</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2018</f>
+              <f>'Time Series'!$A$2:$A$2019</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2018</f>
+              <f>'Time Series'!$C$2:$C$2019</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2018</f>
+              <f>'Time Series'!$A$2:$A$2019</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2018</f>
+              <f>'Time Series'!$E$2:$E$2019</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-09-30 12:00</t>
+          <t>Last Updated: 2026-10-01 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,933</t>
+          <t>25,935</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,925</t>
+          <t>26,050</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,004</t>
+          <t>25,984</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,014</t>
+          <t>25,992</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.45%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.12%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2018"/>
+  <dimension ref="A1:O2019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40704,6 +40704,40 @@
       </c>
       <c r="M2018" t="n">
         <v>25955</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2019" t="n">
+        <v>25935.27</v>
+      </c>
+      <c r="C2019" t="n">
+        <v>26050</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>114.7299999999996</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>0.442370563329395</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2019" t="n">
+        <v>26100</v>
+      </c>
+      <c r="K2019" t="n">
+        <v>25984</v>
+      </c>
+      <c r="L2019" t="n">
+        <v>25992</v>
+      </c>
+      <c r="M2019" t="n">
+        <v>25978</v>
       </c>
     </row>
   </sheetData>
@@ -40731,7 +40765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -41472,6 +41506,22 @@
       </c>
       <c r="D68" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>25935</v>
+      </c>
+      <c r="C69" t="n">
+        <v>26050</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -41525,12 +41575,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,950</t>
+          <t>26,100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41579,12 +41629,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,004</t>
+          <t>25,984</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,014</t>
+          <t>25,992</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41597,12 +41647,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,955</t>
+          <t>25,978</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,955</t>
+          <t>25,978</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2019</f>
+              <f>'Time Series'!$A$2:$A$2020</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2019</f>
+              <f>'Time Series'!$B$2:$B$2020</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2019</f>
+              <f>'Time Series'!$A$2:$A$2020</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2019</f>
+              <f>'Time Series'!$C$2:$C$2020</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2019</f>
+              <f>'Time Series'!$A$2:$A$2020</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2019</f>
+              <f>'Time Series'!$E$2:$E$2020</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-01 12:00</t>
+          <t>Last Updated: 2026-10-02 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,935</t>
+          <t>25,941</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,050</t>
+          <t>25,940</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,984</t>
+          <t>26,006</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,992</t>
+          <t>26,018</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-0.43%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.13%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2019"/>
+  <dimension ref="A1:O2020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40738,6 +40738,40 @@
       </c>
       <c r="M2019" t="n">
         <v>25978</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2020" t="n">
+        <v>25941.35</v>
+      </c>
+      <c r="C2020" t="n">
+        <v>25940</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>-1.349999999998545</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>-0.005204046820996381</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>25920</v>
+      </c>
+      <c r="H2020" t="n">
+        <v>25960</v>
+      </c>
+      <c r="K2020" t="n">
+        <v>26006</v>
+      </c>
+      <c r="L2020" t="n">
+        <v>26018</v>
+      </c>
+      <c r="M2020" t="n">
+        <v>25981</v>
       </c>
     </row>
   </sheetData>
@@ -41515,13 +41549,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25935</v>
+        <v>25938</v>
       </c>
       <c r="C69" t="n">
-        <v>26050</v>
+        <v>25995</v>
       </c>
       <c r="D69" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -41575,12 +41609,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>25,920</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,100</t>
+          <t>25,960</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41611,12 +41645,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,933</t>
+          <t>25,993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,033</t>
+          <t>26,093</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41629,12 +41663,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,984</t>
+          <t>26,006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,992</t>
+          <t>26,018</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41647,12 +41681,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,978</t>
+          <t>25,981</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,978</t>
+          <t>25,981</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2020</f>
+              <f>'Time Series'!$A$2:$A$2021</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2020</f>
+              <f>'Time Series'!$B$2:$B$2021</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2020</f>
+              <f>'Time Series'!$A$2:$A$2021</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2020</f>
+              <f>'Time Series'!$C$2:$C$2021</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2020</f>
+              <f>'Time Series'!$A$2:$A$2021</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2020</f>
+              <f>'Time Series'!$E$2:$E$2021</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-02 12:00</t>
+          <t>Last Updated: 2026-10-03 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,941</t>
+          <t>25,954</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,006</t>
+          <t>26,030</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,018</t>
+          <t>26,043</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.41%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.15%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2020"/>
+  <dimension ref="A1:O2021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40772,6 +40772,40 @@
       </c>
       <c r="M2020" t="n">
         <v>25981</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2021" t="n">
+        <v>25953.96</v>
+      </c>
+      <c r="C2021" t="n">
+        <v>25940</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>-13.95999999999913</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>-0.05378755303621924</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>25920</v>
+      </c>
+      <c r="H2021" t="n">
+        <v>25960</v>
+      </c>
+      <c r="K2021" t="n">
+        <v>26030</v>
+      </c>
+      <c r="L2021" t="n">
+        <v>26043</v>
+      </c>
+      <c r="M2021" t="n">
+        <v>25982</v>
       </c>
     </row>
   </sheetData>
@@ -41549,13 +41583,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25938</v>
+        <v>25944</v>
       </c>
       <c r="C69" t="n">
-        <v>25995</v>
+        <v>25977</v>
       </c>
       <c r="D69" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -41645,12 +41679,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,993</t>
+          <t>26,017</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,093</t>
+          <t>26,127</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41663,12 +41697,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,006</t>
+          <t>26,030</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,018</t>
+          <t>26,043</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41681,12 +41715,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,981</t>
+          <t>25,982</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,981</t>
+          <t>25,982</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2021</f>
+              <f>'Time Series'!$A$2:$A$2022</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2021</f>
+              <f>'Time Series'!$B$2:$B$2022</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2021</f>
+              <f>'Time Series'!$A$2:$A$2022</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2021</f>
+              <f>'Time Series'!$C$2:$C$2022</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2021</f>
+              <f>'Time Series'!$A$2:$A$2022</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2021</f>
+              <f>'Time Series'!$E$2:$E$2022</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-03 12:00</t>
+          <t>Last Updated: 2026-10-04 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,954</t>
+          <t>25,940</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,030</t>
+          <t>26,006</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,043</t>
+          <t>26,018</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.16%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2021"/>
+  <dimension ref="A1:O2022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40805,6 +40805,40 @@
         <v>26043</v>
       </c>
       <c r="M2021" t="n">
+        <v>25982</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B2022" t="n">
+        <v>25939.86</v>
+      </c>
+      <c r="C2022" t="n">
+        <v>25940</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0.1399999999994179</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>0.0005397099290413206</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>25920</v>
+      </c>
+      <c r="H2022" t="n">
+        <v>25960</v>
+      </c>
+      <c r="K2022" t="n">
+        <v>26006</v>
+      </c>
+      <c r="L2022" t="n">
+        <v>26018</v>
+      </c>
+      <c r="M2022" t="n">
         <v>25982</v>
       </c>
     </row>
@@ -41583,13 +41617,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25944</v>
+        <v>25943</v>
       </c>
       <c r="C69" t="n">
-        <v>25977</v>
+        <v>25968</v>
       </c>
       <c r="D69" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -41697,12 +41731,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,030</t>
+          <t>26,006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,043</t>
+          <t>26,018</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2022</f>
+              <f>'Time Series'!$A$2:$A$2023</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2022</f>
+              <f>'Time Series'!$B$2:$B$2023</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2022</f>
+              <f>'Time Series'!$A$2:$A$2023</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2022</f>
+              <f>'Time Series'!$C$2:$C$2023</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2022</f>
+              <f>'Time Series'!$A$2:$A$2023</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2022</f>
+              <f>'Time Series'!$E$2:$E$2023</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-04 12:00</t>
+          <t>Last Updated: 2026-10-05 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>25,949</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>26,015</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,006</t>
+          <t>26,046</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,018</t>
+          <t>26,052</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.34%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.17%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2022"/>
+  <dimension ref="A1:O2023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40840,6 +40840,40 @@
       </c>
       <c r="M2022" t="n">
         <v>25982</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B2023" t="n">
+        <v>25949.12</v>
+      </c>
+      <c r="C2023" t="n">
+        <v>26015</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>65.88000000000102</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>0.2538814418369525</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2023" t="n">
+        <v>26030</v>
+      </c>
+      <c r="K2023" t="n">
+        <v>26046</v>
+      </c>
+      <c r="L2023" t="n">
+        <v>26052</v>
+      </c>
+      <c r="M2023" t="n">
+        <v>25996</v>
       </c>
     </row>
   </sheetData>
@@ -41617,13 +41651,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25943</v>
+        <v>25944</v>
       </c>
       <c r="C69" t="n">
-        <v>25968</v>
+        <v>25977</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -41677,12 +41711,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,960</t>
+          <t>26,030</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41713,12 +41747,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,017</t>
+          <t>26,038</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,127</t>
+          <t>26,138</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41731,12 +41765,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,006</t>
+          <t>26,046</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,018</t>
+          <t>26,052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41749,12 +41783,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,982</t>
+          <t>25,996</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,982</t>
+          <t>25,996</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2023</f>
+              <f>'Time Series'!$A$2:$A$2024</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2023</f>
+              <f>'Time Series'!$B$2:$B$2024</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2023</f>
+              <f>'Time Series'!$A$2:$A$2024</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2023</f>
+              <f>'Time Series'!$C$2:$C$2024</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2023</f>
+              <f>'Time Series'!$A$2:$A$2024</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2023</f>
+              <f>'Time Series'!$E$2:$E$2024</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-05 12:00</t>
+          <t>Last Updated: 2026-10-06 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,949</t>
+          <t>25,966</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,015</t>
+          <t>26,025</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,052</t>
+          <t>26,054</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.31%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2023"/>
+  <dimension ref="A1:O2024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40874,6 +40874,40 @@
       </c>
       <c r="M2023" t="n">
         <v>25996</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2024" t="n">
+        <v>25966.23</v>
+      </c>
+      <c r="C2024" t="n">
+        <v>26025</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>58.77000000000044</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>0.2263324325479688</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2024" t="n">
+        <v>26050</v>
+      </c>
+      <c r="K2024" t="n">
+        <v>26046</v>
+      </c>
+      <c r="L2024" t="n">
+        <v>26054</v>
+      </c>
+      <c r="M2024" t="n">
+        <v>25989</v>
       </c>
     </row>
   </sheetData>
@@ -41651,13 +41685,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25944</v>
+        <v>25948</v>
       </c>
       <c r="C69" t="n">
-        <v>25977</v>
+        <v>25985</v>
       </c>
       <c r="D69" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -41716,7 +41750,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,030</t>
+          <t>26,050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41747,12 +41781,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,038</t>
+          <t>26,059</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,138</t>
+          <t>26,159</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41770,7 +41804,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,052</t>
+          <t>26,054</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41783,12 +41817,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,996</t>
+          <t>25,989</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,996</t>
+          <t>25,989</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2024</f>
+              <f>'Time Series'!$A$2:$A$2025</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2024</f>
+              <f>'Time Series'!$B$2:$B$2025</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2024</f>
+              <f>'Time Series'!$A$2:$A$2025</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2024</f>
+              <f>'Time Series'!$C$2:$C$2025</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2024</f>
+              <f>'Time Series'!$A$2:$A$2025</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2024</f>
+              <f>'Time Series'!$E$2:$E$2025</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-06 12:00</t>
+          <t>Last Updated: 2026-10-07 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,966</t>
+          <t>25,936</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,025</t>
+          <t>26,090</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,046</t>
+          <t>26,060</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,054</t>
+          <t>26,066</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2024"/>
+  <dimension ref="A1:O2025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40908,6 +40908,40 @@
       </c>
       <c r="M2024" t="n">
         <v>25989</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2025" t="n">
+        <v>25935.9</v>
+      </c>
+      <c r="C2025" t="n">
+        <v>26090</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>154.0999999999985</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>0.5941571335484735</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>26040</v>
+      </c>
+      <c r="H2025" t="n">
+        <v>26140</v>
+      </c>
+      <c r="K2025" t="n">
+        <v>26060</v>
+      </c>
+      <c r="L2025" t="n">
+        <v>26066</v>
+      </c>
+      <c r="M2025" t="n">
+        <v>25976</v>
       </c>
     </row>
   </sheetData>
@@ -41685,13 +41719,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25948</v>
+        <v>25946</v>
       </c>
       <c r="C69" t="n">
-        <v>25985</v>
+        <v>26000</v>
       </c>
       <c r="D69" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -41745,12 +41779,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>26,040</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,050</t>
+          <t>26,140</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41781,12 +41815,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,059</t>
+          <t>26,064</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,159</t>
+          <t>26,164</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41799,12 +41833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,046</t>
+          <t>26,060</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,054</t>
+          <t>26,066</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41817,12 +41851,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,989</t>
+          <t>25,976</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,989</t>
+          <t>25,976</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2025</f>
+              <f>'Time Series'!$A$2:$A$2026</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2025</f>
+              <f>'Time Series'!$B$2:$B$2026</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2025</f>
+              <f>'Time Series'!$A$2:$A$2026</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2025</f>
+              <f>'Time Series'!$C$2:$C$2026</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2025</f>
+              <f>'Time Series'!$A$2:$A$2026</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2025</f>
+              <f>'Time Series'!$E$2:$E$2026</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-07 12:00</t>
+          <t>Last Updated: 2026-10-08 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,936</t>
+          <t>25,953</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,060</t>
+          <t>26,022</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,066</t>
+          <t>26,034</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.20%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2025"/>
+  <dimension ref="A1:O2026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40942,6 +40942,40 @@
       </c>
       <c r="M2025" t="n">
         <v>25976</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2026" t="n">
+        <v>25952.99</v>
+      </c>
+      <c r="C2026" t="n">
+        <v>26090</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>137.0099999999984</v>
+      </c>
+      <c r="E2026" t="n">
+        <v>0.5279160512911938</v>
+      </c>
+      <c r="G2026" t="n">
+        <v>26040</v>
+      </c>
+      <c r="H2026" t="n">
+        <v>26140</v>
+      </c>
+      <c r="K2026" t="n">
+        <v>26022</v>
+      </c>
+      <c r="L2026" t="n">
+        <v>26034</v>
+      </c>
+      <c r="M2026" t="n">
+        <v>25881</v>
       </c>
     </row>
   </sheetData>
@@ -41719,13 +41753,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25946</v>
+        <v>25947</v>
       </c>
       <c r="C69" t="n">
-        <v>26000</v>
+        <v>26011</v>
       </c>
       <c r="D69" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -41815,12 +41849,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,064</t>
+          <t>26,103</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,164</t>
+          <t>26,203</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41833,12 +41867,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,060</t>
+          <t>26,022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,066</t>
+          <t>26,034</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41851,12 +41885,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,976</t>
+          <t>25,881</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,976</t>
+          <t>25,881</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2026</f>
+              <f>'Time Series'!$A$2:$A$2027</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2026</f>
+              <f>'Time Series'!$B$2:$B$2027</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2026</f>
+              <f>'Time Series'!$A$2:$A$2027</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2026</f>
+              <f>'Time Series'!$C$2:$C$2027</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2026</f>
+              <f>'Time Series'!$A$2:$A$2027</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2026</f>
+              <f>'Time Series'!$E$2:$E$2027</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-08 12:00</t>
+          <t>Last Updated: 2026-10-09 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,953</t>
+          <t>25,868</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,090</t>
+          <t>26,130</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,022</t>
+          <t>26,051</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,034</t>
+          <t>26,068</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.15%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2026"/>
+  <dimension ref="A1:O2027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40976,6 +40976,40 @@
       </c>
       <c r="M2026" t="n">
         <v>25881</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2027" t="n">
+        <v>25868.38</v>
+      </c>
+      <c r="C2027" t="n">
+        <v>26130</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>261.619999999999</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>1.011350536832994</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>26080</v>
+      </c>
+      <c r="H2027" t="n">
+        <v>26180</v>
+      </c>
+      <c r="K2027" t="n">
+        <v>26051</v>
+      </c>
+      <c r="L2027" t="n">
+        <v>26068</v>
+      </c>
+      <c r="M2027" t="n">
+        <v>25859</v>
       </c>
     </row>
   </sheetData>
@@ -41753,13 +41787,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25947</v>
+        <v>25938</v>
       </c>
       <c r="C69" t="n">
-        <v>26011</v>
+        <v>26024</v>
       </c>
       <c r="D69" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -41813,12 +41847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,040</t>
+          <t>26,080</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,140</t>
+          <t>26,180</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41849,12 +41883,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,103</t>
+          <t>26,065</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,203</t>
+          <t>26,165</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41867,12 +41901,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,022</t>
+          <t>26,051</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,034</t>
+          <t>26,068</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41885,12 +41919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,881</t>
+          <t>25,859</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,881</t>
+          <t>25,859</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2027</f>
+              <f>'Time Series'!$A$2:$A$2028</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2027</f>
+              <f>'Time Series'!$B$2:$B$2028</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2027</f>
+              <f>'Time Series'!$A$2:$A$2028</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2027</f>
+              <f>'Time Series'!$C$2:$C$2028</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2027</f>
+              <f>'Time Series'!$A$2:$A$2028</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2027</f>
+              <f>'Time Series'!$E$2:$E$2028</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-09 12:00</t>
+          <t>Last Updated: 2026-10-10 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,868</t>
+          <t>25,863</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,130</t>
+          <t>26,120</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,051</t>
+          <t>26,086</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,068</t>
+          <t>26,100</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.10%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2027"/>
+  <dimension ref="A1:O2028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41010,6 +41010,40 @@
       </c>
       <c r="M2027" t="n">
         <v>25859</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2028" t="n">
+        <v>25862.65</v>
+      </c>
+      <c r="C2028" t="n">
+        <v>26120</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>257.3499999999985</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>0.9950643108884765</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>26070</v>
+      </c>
+      <c r="H2028" t="n">
+        <v>26170</v>
+      </c>
+      <c r="K2028" t="n">
+        <v>26086</v>
+      </c>
+      <c r="L2028" t="n">
+        <v>26100</v>
+      </c>
+      <c r="M2028" t="n">
+        <v>25876</v>
       </c>
     </row>
   </sheetData>
@@ -41787,13 +41821,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25938</v>
+        <v>25931</v>
       </c>
       <c r="C69" t="n">
-        <v>26024</v>
+        <v>26034</v>
       </c>
       <c r="D69" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -41847,12 +41881,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,080</t>
+          <t>26,070</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,180</t>
+          <t>26,170</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41883,12 +41917,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,065</t>
+          <t>25,970</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,165</t>
+          <t>26,070</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41901,12 +41935,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,051</t>
+          <t>26,086</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,068</t>
+          <t>26,100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41919,12 +41953,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,859</t>
+          <t>25,876</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,859</t>
+          <t>25,876</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2028</f>
+              <f>'Time Series'!$A$2:$A$2029</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2028</f>
+              <f>'Time Series'!$B$2:$B$2029</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2028</f>
+              <f>'Time Series'!$A$2:$A$2029</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2028</f>
+              <f>'Time Series'!$C$2:$C$2029</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2028</f>
+              <f>'Time Series'!$A$2:$A$2029</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2028</f>
+              <f>'Time Series'!$E$2:$E$2029</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-10 12:00</t>
+          <t>Last Updated: 2026-10-11 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,863</t>
+          <t>25,856</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,086</t>
+          <t>26,073</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,100</t>
+          <t>26,098</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.05%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2028"/>
+  <dimension ref="A1:O2029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41044,6 +41044,40 @@
       </c>
       <c r="M2028" t="n">
         <v>25876</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B2029" t="n">
+        <v>25855.72</v>
+      </c>
+      <c r="C2029" t="n">
+        <v>26120</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>264.2799999999988</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>1.022133593649679</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>26070</v>
+      </c>
+      <c r="H2029" t="n">
+        <v>26170</v>
+      </c>
+      <c r="K2029" t="n">
+        <v>26073</v>
+      </c>
+      <c r="L2029" t="n">
+        <v>26098</v>
+      </c>
+      <c r="M2029" t="n">
+        <v>25875</v>
       </c>
     </row>
   </sheetData>
@@ -41821,13 +41855,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25931</v>
+        <v>25924</v>
       </c>
       <c r="C69" t="n">
-        <v>26034</v>
+        <v>26042</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -41935,12 +41969,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,086</t>
+          <t>26,073</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,100</t>
+          <t>26,098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41953,12 +41987,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,876</t>
+          <t>25,875</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,876</t>
+          <t>25,875</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2029</f>
+              <f>'Time Series'!$A$2:$A$2030</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2029</f>
+              <f>'Time Series'!$B$2:$B$2030</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2029</f>
+              <f>'Time Series'!$A$2:$A$2030</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2029</f>
+              <f>'Time Series'!$C$2:$C$2030</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2029</f>
+              <f>'Time Series'!$A$2:$A$2030</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2029</f>
+              <f>'Time Series'!$E$2:$E$2030</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-11 12:00</t>
+          <t>Last Updated: 2026-10-12 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,856</t>
+          <t>25,886</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,120</t>
+          <t>26,135</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,073</t>
+          <t>26,028</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,098</t>
+          <t>26,065</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2029"/>
+  <dimension ref="A1:O2030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41078,6 +41078,40 @@
       </c>
       <c r="M2029" t="n">
         <v>25875</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2030" t="n">
+        <v>25886.36</v>
+      </c>
+      <c r="C2030" t="n">
+        <v>26135</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>248.6399999999994</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>0.9605058416865075</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>26110</v>
+      </c>
+      <c r="H2030" t="n">
+        <v>26160</v>
+      </c>
+      <c r="K2030" t="n">
+        <v>26028</v>
+      </c>
+      <c r="L2030" t="n">
+        <v>26065</v>
+      </c>
+      <c r="M2030" t="n">
+        <v>25920</v>
       </c>
     </row>
   </sheetData>
@@ -41855,13 +41889,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25924</v>
+        <v>25921</v>
       </c>
       <c r="C69" t="n">
-        <v>26042</v>
+        <v>26050</v>
       </c>
       <c r="D69" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -41915,12 +41949,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,070</t>
+          <t>26,110</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,170</t>
+          <t>26,160</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -41951,12 +41985,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,970</t>
+          <t>25,993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,070</t>
+          <t>26,093</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -41969,12 +42003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,073</t>
+          <t>26,028</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,098</t>
+          <t>26,065</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -41987,12 +42021,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,875</t>
+          <t>25,920</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,875</t>
+          <t>25,920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2030</f>
+              <f>'Time Series'!$A$2:$A$2031</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2030</f>
+              <f>'Time Series'!$B$2:$B$2031</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2030</f>
+              <f>'Time Series'!$A$2:$A$2031</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2030</f>
+              <f>'Time Series'!$C$2:$C$2031</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2030</f>
+              <f>'Time Series'!$A$2:$A$2031</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2030</f>
+              <f>'Time Series'!$E$2:$E$2031</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-12 12:00</t>
+          <t>Last Updated: 2026-10-13 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,886</t>
+          <t>25,897</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,028</t>
+          <t>26,026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,065</t>
+          <t>26,052</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2030"/>
+  <dimension ref="A1:O2031"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41112,6 +41112,40 @@
       </c>
       <c r="M2030" t="n">
         <v>25920</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2031" t="n">
+        <v>25897.06</v>
+      </c>
+      <c r="C2031" t="n">
+        <v>26135</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>237.9399999999987</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>0.9187915539447283</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>26110</v>
+      </c>
+      <c r="H2031" t="n">
+        <v>26160</v>
+      </c>
+      <c r="K2031" t="n">
+        <v>26026</v>
+      </c>
+      <c r="L2031" t="n">
+        <v>26052</v>
+      </c>
+      <c r="M2031" t="n">
+        <v>25895</v>
       </c>
     </row>
   </sheetData>
@@ -41889,13 +41923,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25921</v>
+        <v>25919</v>
       </c>
       <c r="C69" t="n">
-        <v>26050</v>
+        <v>26056</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -41985,12 +42019,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,993</t>
+          <t>26,015</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,093</t>
+          <t>26,115</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42003,12 +42037,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,028</t>
+          <t>26,026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,065</t>
+          <t>26,052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42021,12 +42055,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>25,895</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>25,895</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2031</f>
+              <f>'Time Series'!$A$2:$A$2032</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2031</f>
+              <f>'Time Series'!$B$2:$B$2032</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2031</f>
+              <f>'Time Series'!$A$2:$A$2032</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2031</f>
+              <f>'Time Series'!$C$2:$C$2032</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2031</f>
+              <f>'Time Series'!$A$2:$A$2032</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2031</f>
+              <f>'Time Series'!$E$2:$E$2032</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-13 12:00</t>
+          <t>Last Updated: 2026-10-14 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,135</t>
+          <t>26,025</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,026</t>
+          <t>25,990</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,052</t>
+          <t>26,011</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2031"/>
+  <dimension ref="A1:O2032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41146,6 +41146,40 @@
       </c>
       <c r="M2031" t="n">
         <v>25895</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2032" t="n">
+        <v>25897.09</v>
+      </c>
+      <c r="C2032" t="n">
+        <v>26025</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>127.9099999999999</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>0.4939164979540166</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2032" t="n">
+        <v>26050</v>
+      </c>
+      <c r="K2032" t="n">
+        <v>25990</v>
+      </c>
+      <c r="L2032" t="n">
+        <v>26011</v>
+      </c>
+      <c r="M2032" t="n">
+        <v>25878</v>
       </c>
     </row>
   </sheetData>
@@ -41923,10 +41957,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25919</v>
+        <v>25917</v>
       </c>
       <c r="C69" t="n">
-        <v>26056</v>
+        <v>26054</v>
       </c>
       <c r="D69" t="n">
         <v>0.53</v>
@@ -41983,12 +42017,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,110</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,160</t>
+          <t>26,050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42019,12 +42053,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,015</t>
+          <t>26,040</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,115</t>
+          <t>26,140</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42037,12 +42071,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,026</t>
+          <t>25,990</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,052</t>
+          <t>26,011</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42055,12 +42089,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,895</t>
+          <t>25,878</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,895</t>
+          <t>25,878</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2032</f>
+              <f>'Time Series'!$A$2:$A$2033</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2032</f>
+              <f>'Time Series'!$B$2:$B$2033</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2032</f>
+              <f>'Time Series'!$A$2:$A$2033</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2032</f>
+              <f>'Time Series'!$C$2:$C$2033</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2032</f>
+              <f>'Time Series'!$A$2:$A$2033</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2032</f>
+              <f>'Time Series'!$E$2:$E$2033</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-14 12:00</t>
+          <t>Last Updated: 2026-10-15 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,897</t>
+          <t>25,890</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,990</t>
+          <t>25,930</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,011</t>
+          <t>25,940</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2032"/>
+  <dimension ref="A1:O2033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41180,6 +41180,40 @@
       </c>
       <c r="M2032" t="n">
         <v>25878</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2033" t="n">
+        <v>25890.2</v>
+      </c>
+      <c r="C2033" t="n">
+        <v>26025</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>134.7999999999993</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>0.5206603270735617</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2033" t="n">
+        <v>26050</v>
+      </c>
+      <c r="K2033" t="n">
+        <v>25930</v>
+      </c>
+      <c r="L2033" t="n">
+        <v>25940</v>
+      </c>
+      <c r="M2033" t="n">
+        <v>25849</v>
       </c>
     </row>
   </sheetData>
@@ -41957,10 +41991,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25917</v>
+        <v>25915</v>
       </c>
       <c r="C69" t="n">
-        <v>26054</v>
+        <v>26052</v>
       </c>
       <c r="D69" t="n">
         <v>0.53</v>
@@ -42053,12 +42087,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,040</t>
+          <t>26,036</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,140</t>
+          <t>26,136</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42071,12 +42105,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,990</t>
+          <t>25,930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,011</t>
+          <t>25,940</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42089,12 +42123,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,878</t>
+          <t>25,849</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,878</t>
+          <t>25,849</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2033</f>
+              <f>'Time Series'!$A$2:$A$2034</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2033</f>
+              <f>'Time Series'!$B$2:$B$2034</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2033</f>
+              <f>'Time Series'!$A$2:$A$2034</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2033</f>
+              <f>'Time Series'!$C$2:$C$2034</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2033</f>
+              <f>'Time Series'!$A$2:$A$2034</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2033</f>
+              <f>'Time Series'!$E$2:$E$2034</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-15 12:00</t>
+          <t>Last Updated: 2026-10-16 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,890</t>
+          <t>25,856</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,025</t>
+          <t>25,935</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,930</t>
+          <t>25,882</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>25,965</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.18%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2033"/>
+  <dimension ref="A1:O2034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41214,6 +41214,40 @@
       </c>
       <c r="M2033" t="n">
         <v>25849</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2034" t="n">
+        <v>25856.49</v>
+      </c>
+      <c r="C2034" t="n">
+        <v>25935</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>78.5099999999984</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>0.3036375006816409</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>25910</v>
+      </c>
+      <c r="H2034" t="n">
+        <v>25960</v>
+      </c>
+      <c r="K2034" t="n">
+        <v>25882</v>
+      </c>
+      <c r="L2034" t="n">
+        <v>25965</v>
+      </c>
+      <c r="M2034" t="n">
+        <v>25873</v>
       </c>
     </row>
   </sheetData>
@@ -41991,13 +42025,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25915</v>
+        <v>25912</v>
       </c>
       <c r="C69" t="n">
-        <v>26052</v>
+        <v>26045</v>
       </c>
       <c r="D69" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -42051,12 +42085,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>25,910</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,050</t>
+          <t>25,960</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42087,12 +42121,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,036</t>
+          <t>26,033</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,136</t>
+          <t>26,133</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42105,12 +42139,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,930</t>
+          <t>25,882</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>25,965</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42123,12 +42157,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,849</t>
+          <t>25,873</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,849</t>
+          <t>25,873</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2034</f>
+              <f>'Time Series'!$A$2:$A$2035</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2034</f>
+              <f>'Time Series'!$B$2:$B$2035</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2034</f>
+              <f>'Time Series'!$A$2:$A$2035</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2034</f>
+              <f>'Time Series'!$C$2:$C$2035</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2034</f>
+              <f>'Time Series'!$A$2:$A$2035</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2034</f>
+              <f>'Time Series'!$E$2:$E$2035</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-16 12:00</t>
+          <t>Last Updated: 2026-10-17 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,856</t>
+          <t>25,869</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,935</t>
+          <t>25,950</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,882</t>
+          <t>26,047</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,965</t>
+          <t>26,094</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.19%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2034"/>
+  <dimension ref="A1:O2035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41248,6 +41248,40 @@
       </c>
       <c r="M2034" t="n">
         <v>25873</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2035" t="n">
+        <v>25868.9</v>
+      </c>
+      <c r="C2035" t="n">
+        <v>25950</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>81.09999999999854</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>0.3135038598471467</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>25900</v>
+      </c>
+      <c r="H2035" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K2035" t="n">
+        <v>26047</v>
+      </c>
+      <c r="L2035" t="n">
+        <v>26094</v>
+      </c>
+      <c r="M2035" t="n">
+        <v>25864</v>
       </c>
     </row>
   </sheetData>
@@ -42025,13 +42059,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25912</v>
+        <v>25909</v>
       </c>
       <c r="C69" t="n">
-        <v>26045</v>
+        <v>26039</v>
       </c>
       <c r="D69" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -42085,12 +42119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,910</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25,960</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42121,12 +42155,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,033</t>
+          <t>26,038</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,133</t>
+          <t>26,138</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42139,12 +42173,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,882</t>
+          <t>26,047</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,965</t>
+          <t>26,094</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42157,12 +42191,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,873</t>
+          <t>25,864</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,873</t>
+          <t>25,864</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2035</f>
+              <f>'Time Series'!$A$2:$A$2036</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2035</f>
+              <f>'Time Series'!$B$2:$B$2036</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2035</f>
+              <f>'Time Series'!$A$2:$A$2036</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2035</f>
+              <f>'Time Series'!$C$2:$C$2036</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2035</f>
+              <f>'Time Series'!$A$2:$A$2036</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2035</f>
+              <f>'Time Series'!$E$2:$E$2036</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-17 12:00</t>
+          <t>Last Updated: 2026-10-18 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,869</t>
+          <t>25,861</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,047</t>
+          <t>26,030</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,094</t>
+          <t>26,076</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.20%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2035"/>
+  <dimension ref="A1:O2036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41282,6 +41282,40 @@
       </c>
       <c r="M2035" t="n">
         <v>25864</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2036" t="n">
+        <v>25860.56</v>
+      </c>
+      <c r="C2036" t="n">
+        <v>25950</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>89.43999999999869</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>0.3458548461440846</v>
+      </c>
+      <c r="G2036" t="n">
+        <v>25900</v>
+      </c>
+      <c r="H2036" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K2036" t="n">
+        <v>26030</v>
+      </c>
+      <c r="L2036" t="n">
+        <v>26076</v>
+      </c>
+      <c r="M2036" t="n">
+        <v>25868</v>
       </c>
     </row>
   </sheetData>
@@ -42059,13 +42093,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25909</v>
+        <v>25907</v>
       </c>
       <c r="C69" t="n">
-        <v>26039</v>
+        <v>26034</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -42173,12 +42207,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,047</t>
+          <t>26,030</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,094</t>
+          <t>26,076</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42191,12 +42225,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,864</t>
+          <t>25,868</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,864</t>
+          <t>25,868</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2036</f>
+              <f>'Time Series'!$A$2:$A$2037</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2036</f>
+              <f>'Time Series'!$B$2:$B$2037</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2036</f>
+              <f>'Time Series'!$A$2:$A$2037</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2036</f>
+              <f>'Time Series'!$C$2:$C$2037</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2036</f>
+              <f>'Time Series'!$A$2:$A$2037</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2036</f>
+              <f>'Time Series'!$E$2:$E$2037</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-18 12:00</t>
+          <t>Last Updated: 2026-10-19 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,861</t>
+          <t>25,869</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,950</t>
+          <t>26,025</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,030</t>
+          <t>25,958</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,076</t>
+          <t>26,014</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.19%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2036"/>
+  <dimension ref="A1:O2037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41316,6 +41316,40 @@
       </c>
       <c r="M2036" t="n">
         <v>25868</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2037" t="n">
+        <v>25869.4</v>
+      </c>
+      <c r="C2037" t="n">
+        <v>26025</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>155.5999999999985</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>0.6014828329996</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2037" t="n">
+        <v>26050</v>
+      </c>
+      <c r="K2037" t="n">
+        <v>25958</v>
+      </c>
+      <c r="L2037" t="n">
+        <v>26014</v>
+      </c>
+      <c r="M2037" t="n">
+        <v>25879</v>
       </c>
     </row>
   </sheetData>
@@ -42093,13 +42127,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25907</v>
+        <v>25905</v>
       </c>
       <c r="C69" t="n">
         <v>26034</v>
       </c>
       <c r="D69" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -42153,12 +42187,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>26,050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42189,12 +42223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,038</t>
+          <t>26,010</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,138</t>
+          <t>26,110</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42207,12 +42241,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,030</t>
+          <t>25,958</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,076</t>
+          <t>26,014</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42225,12 +42259,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,868</t>
+          <t>25,879</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,868</t>
+          <t>25,879</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2037</f>
+              <f>'Time Series'!$A$2:$A$2038</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2037</f>
+              <f>'Time Series'!$B$2:$B$2038</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2037</f>
+              <f>'Time Series'!$A$2:$A$2038</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2037</f>
+              <f>'Time Series'!$C$2:$C$2038</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2037</f>
+              <f>'Time Series'!$A$2:$A$2038</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2037</f>
+              <f>'Time Series'!$E$2:$E$2038</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-19 12:00</t>
+          <t>Last Updated: 2026-10-20 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,869</t>
+          <t>25,858</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,025</t>
+          <t>26,040</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,958</t>
+          <t>25,968</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,014</t>
+          <t>26,033</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2037"/>
+  <dimension ref="A1:O2038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41350,6 +41350,40 @@
       </c>
       <c r="M2037" t="n">
         <v>25879</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2038" t="n">
+        <v>25857.68</v>
+      </c>
+      <c r="C2038" t="n">
+        <v>26040</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>182.3199999999997</v>
+      </c>
+      <c r="E2038" t="n">
+        <v>0.7050903251954533</v>
+      </c>
+      <c r="G2038" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2038" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2038" t="n">
+        <v>25968</v>
+      </c>
+      <c r="L2038" t="n">
+        <v>26033</v>
+      </c>
+      <c r="M2038" t="n">
+        <v>25853</v>
       </c>
     </row>
   </sheetData>
@@ -42127,13 +42161,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25905</v>
+        <v>25902</v>
       </c>
       <c r="C69" t="n">
         <v>26034</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -42192,7 +42226,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,050</t>
+          <t>26,080</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42223,12 +42257,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,010</t>
+          <t>25,949</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,110</t>
+          <t>26,049</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42241,12 +42275,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,958</t>
+          <t>25,968</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,014</t>
+          <t>26,033</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42259,12 +42293,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,879</t>
+          <t>25,853</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,879</t>
+          <t>25,853</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2038</f>
+              <f>'Time Series'!$A$2:$A$2039</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2038</f>
+              <f>'Time Series'!$B$2:$B$2039</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2038</f>
+              <f>'Time Series'!$A$2:$A$2039</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2038</f>
+              <f>'Time Series'!$C$2:$C$2039</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2038</f>
+              <f>'Time Series'!$A$2:$A$2039</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2038</f>
+              <f>'Time Series'!$E$2:$E$2039</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-20 12:00</t>
+          <t>Last Updated: 2026-10-21 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,858</t>
+          <t>25,846</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,968</t>
+          <t>26,000</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,033</t>
+          <t>26,029</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2038"/>
+  <dimension ref="A1:O2039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41384,6 +41384,40 @@
       </c>
       <c r="M2038" t="n">
         <v>25853</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2039" t="n">
+        <v>25846.2</v>
+      </c>
+      <c r="C2039" t="n">
+        <v>26040</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>193.7999999999993</v>
+      </c>
+      <c r="E2039" t="n">
+        <v>0.74982008960698</v>
+      </c>
+      <c r="G2039" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2039" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2039" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L2039" t="n">
+        <v>26029</v>
+      </c>
+      <c r="M2039" t="n">
+        <v>25832</v>
       </c>
     </row>
   </sheetData>
@@ -42161,13 +42195,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25902</v>
+        <v>25900</v>
       </c>
       <c r="C69" t="n">
         <v>26034</v>
       </c>
       <c r="D69" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -42275,12 +42309,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,968</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,033</t>
+          <t>26,029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42293,12 +42327,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,853</t>
+          <t>25,832</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,853</t>
+          <t>25,832</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2039</f>
+              <f>'Time Series'!$A$2:$A$2040</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2039</f>
+              <f>'Time Series'!$B$2:$B$2040</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2039</f>
+              <f>'Time Series'!$A$2:$A$2040</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2039</f>
+              <f>'Time Series'!$C$2:$C$2040</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2039</f>
+              <f>'Time Series'!$A$2:$A$2040</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2039</f>
+              <f>'Time Series'!$E$2:$E$2040</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-21 12:00</t>
+          <t>Last Updated: 2026-10-22 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,846</t>
+          <t>25,847</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>26,164</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,029</t>
+          <t>26,077</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.18%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2039"/>
+  <dimension ref="A1:O2040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41418,6 +41418,40 @@
       </c>
       <c r="M2039" t="n">
         <v>25832</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2040" t="n">
+        <v>25846.7</v>
+      </c>
+      <c r="C2040" t="n">
+        <v>26040</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>193.2999999999993</v>
+      </c>
+      <c r="E2040" t="n">
+        <v>0.7478711015332684</v>
+      </c>
+      <c r="G2040" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2040" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2040" t="n">
+        <v>26164</v>
+      </c>
+      <c r="L2040" t="n">
+        <v>26077</v>
+      </c>
+      <c r="M2040" t="n">
+        <v>25833</v>
       </c>
     </row>
   </sheetData>
@@ -42195,13 +42229,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25900</v>
+        <v>25897</v>
       </c>
       <c r="C69" t="n">
-        <v>26034</v>
+        <v>26035</v>
       </c>
       <c r="D69" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -42291,12 +42325,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,949</t>
+          <t>25,967</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,049</t>
+          <t>26,067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42309,12 +42343,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>26,164</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,029</t>
+          <t>26,077</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42327,12 +42361,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,832</t>
+          <t>25,833</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,832</t>
+          <t>25,833</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2040</f>
+              <f>'Time Series'!$A$2:$A$2041</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2040</f>
+              <f>'Time Series'!$B$2:$B$2041</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2040</f>
+              <f>'Time Series'!$A$2:$A$2041</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2040</f>
+              <f>'Time Series'!$C$2:$C$2041</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2040</f>
+              <f>'Time Series'!$A$2:$A$2041</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2040</f>
+              <f>'Time Series'!$E$2:$E$2041</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-22 12:00</t>
+          <t>Last Updated: 2026-10-23 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,847</t>
+          <t>25,831</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,164</t>
+          <t>26,094</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,077</t>
+          <t>26,132</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2040"/>
+  <dimension ref="A1:O2041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41452,6 +41452,40 @@
       </c>
       <c r="M2040" t="n">
         <v>25833</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2041" t="n">
+        <v>25831.15</v>
+      </c>
+      <c r="C2041" t="n">
+        <v>26040</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>208.8499999999985</v>
+      </c>
+      <c r="E2041" t="n">
+        <v>0.8085199458792913</v>
+      </c>
+      <c r="G2041" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2041" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2041" t="n">
+        <v>26094</v>
+      </c>
+      <c r="L2041" t="n">
+        <v>26132</v>
+      </c>
+      <c r="M2041" t="n">
+        <v>25817</v>
       </c>
     </row>
   </sheetData>
@@ -42229,13 +42263,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25897</v>
+        <v>25894</v>
       </c>
       <c r="C69" t="n">
         <v>26035</v>
       </c>
       <c r="D69" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -42325,12 +42359,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,967</t>
+          <t>25,940</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,067</t>
+          <t>26,040</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42343,12 +42377,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,164</t>
+          <t>26,094</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,077</t>
+          <t>26,132</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42361,12 +42395,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,833</t>
+          <t>25,817</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,833</t>
+          <t>25,817</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2041</f>
+              <f>'Time Series'!$A$2:$A$2042</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2041</f>
+              <f>'Time Series'!$B$2:$B$2042</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2041</f>
+              <f>'Time Series'!$A$2:$A$2042</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2041</f>
+              <f>'Time Series'!$C$2:$C$2042</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2041</f>
+              <f>'Time Series'!$A$2:$A$2042</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2041</f>
+              <f>'Time Series'!$E$2:$E$2042</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-23 12:00</t>
+          <t>Last Updated: 2026-10-24 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,831</t>
+          <t>25,822</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,094</t>
+          <t>26,334</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,132</t>
+          <t>26,264</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2041"/>
+  <dimension ref="A1:O2042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41486,6 +41486,40 @@
       </c>
       <c r="M2041" t="n">
         <v>25817</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2042" t="n">
+        <v>25822.18</v>
+      </c>
+      <c r="C2042" t="n">
+        <v>26040</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>217.8199999999997</v>
+      </c>
+      <c r="E2042" t="n">
+        <v>0.8435383844431404</v>
+      </c>
+      <c r="G2042" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H2042" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2042" t="n">
+        <v>26334</v>
+      </c>
+      <c r="L2042" t="n">
+        <v>26264</v>
+      </c>
+      <c r="M2042" t="n">
+        <v>25819</v>
       </c>
     </row>
   </sheetData>
@@ -42263,13 +42297,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25894</v>
+        <v>25891</v>
       </c>
       <c r="C69" t="n">
         <v>26035</v>
       </c>
       <c r="D69" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -42359,12 +42393,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,940</t>
+          <t>25,957</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,040</t>
+          <t>26,057</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42377,12 +42411,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,094</t>
+          <t>26,334</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,132</t>
+          <t>26,264</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42395,12 +42429,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,817</t>
+          <t>25,819</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,817</t>
+          <t>25,819</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2042</f>
+              <f>'Time Series'!$A$2:$A$2043</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2042</f>
+              <f>'Time Series'!$B$2:$B$2043</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2042</f>
+              <f>'Time Series'!$A$2:$A$2043</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2042</f>
+              <f>'Time Series'!$C$2:$C$2043</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2042</f>
+              <f>'Time Series'!$A$2:$A$2043</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2042</f>
+              <f>'Time Series'!$E$2:$E$2043</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-24 12:00</t>
+          <t>Last Updated: 2026-10-25 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,817</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,040</t>
+          <t>26,385</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,334</t>
+          <t>26,352</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,264</t>
+          <t>26,292</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.16%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2042"/>
+  <dimension ref="A1:O2043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41520,6 +41520,40 @@
       </c>
       <c r="M2042" t="n">
         <v>25819</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2043" t="n">
+        <v>25817.34</v>
+      </c>
+      <c r="C2043" t="n">
+        <v>26385</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>567.6599999999999</v>
+      </c>
+      <c r="E2043" t="n">
+        <v>2.198754790385066</v>
+      </c>
+      <c r="G2043" t="n">
+        <v>26360</v>
+      </c>
+      <c r="H2043" t="n">
+        <v>26410</v>
+      </c>
+      <c r="K2043" t="n">
+        <v>26352</v>
+      </c>
+      <c r="L2043" t="n">
+        <v>26292</v>
+      </c>
+      <c r="M2043" t="n">
+        <v>25820</v>
       </c>
     </row>
   </sheetData>
@@ -42297,13 +42331,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25891</v>
+        <v>25888</v>
       </c>
       <c r="C69" t="n">
-        <v>26035</v>
+        <v>26049</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -42357,12 +42391,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>26,360</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,080</t>
+          <t>26,410</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42411,12 +42445,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,334</t>
+          <t>26,352</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,264</t>
+          <t>26,292</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42429,12 +42463,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,819</t>
+          <t>25,820</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,819</t>
+          <t>25,820</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2043</f>
+              <f>'Time Series'!$A$2:$A$2044</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2043</f>
+              <f>'Time Series'!$B$2:$B$2044</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2043</f>
+              <f>'Time Series'!$A$2:$A$2044</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2043</f>
+              <f>'Time Series'!$C$2:$C$2044</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2043</f>
+              <f>'Time Series'!$A$2:$A$2044</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2043</f>
+              <f>'Time Series'!$E$2:$E$2044</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-25 12:00</t>
+          <t>Last Updated: 2026-10-26 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,817</t>
+          <t>25,830</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,385</t>
+          <t>26,450</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,352</t>
+          <t>26,102</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,292</t>
+          <t>26,170</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.14%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2043"/>
+  <dimension ref="A1:O2044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41554,6 +41554,40 @@
       </c>
       <c r="M2043" t="n">
         <v>25820</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2044" t="n">
+        <v>25829.65</v>
+      </c>
+      <c r="C2044" t="n">
+        <v>26450</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>620.3499999999985</v>
+      </c>
+      <c r="E2044" t="n">
+        <v>2.401697274256517</v>
+      </c>
+      <c r="G2044" t="n">
+        <v>26400</v>
+      </c>
+      <c r="H2044" t="n">
+        <v>26500</v>
+      </c>
+      <c r="K2044" t="n">
+        <v>26102</v>
+      </c>
+      <c r="L2044" t="n">
+        <v>26170</v>
+      </c>
+      <c r="M2044" t="n">
+        <v>25824</v>
       </c>
     </row>
   </sheetData>
@@ -42331,13 +42365,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25888</v>
+        <v>25886</v>
       </c>
       <c r="C69" t="n">
-        <v>26049</v>
+        <v>26064</v>
       </c>
       <c r="D69" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -42391,12 +42425,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,360</t>
+          <t>26,400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,410</t>
+          <t>26,500</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42427,12 +42461,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,957</t>
+          <t>25,967</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,057</t>
+          <t>26,067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42445,12 +42479,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,352</t>
+          <t>26,102</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,292</t>
+          <t>26,170</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42463,12 +42497,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,820</t>
+          <t>25,824</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,820</t>
+          <t>25,824</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2044</f>
+              <f>'Time Series'!$A$2:$A$2045</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2044</f>
+              <f>'Time Series'!$B$2:$B$2045</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2044</f>
+              <f>'Time Series'!$A$2:$A$2045</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2044</f>
+              <f>'Time Series'!$C$2:$C$2045</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2044</f>
+              <f>'Time Series'!$A$2:$A$2045</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2044</f>
+              <f>'Time Series'!$E$2:$E$2045</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-26 12:00</t>
+          <t>Last Updated: 2026-10-27 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,830</t>
+          <t>25,832</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,450</t>
+          <t>26,115</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,102</t>
+          <t>26,044</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,170</t>
+          <t>26,107</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.13%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2044"/>
+  <dimension ref="A1:O2045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41588,6 +41588,40 @@
       </c>
       <c r="M2044" t="n">
         <v>25824</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2045" t="n">
+        <v>25831.55</v>
+      </c>
+      <c r="C2045" t="n">
+        <v>26115</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>283.4500000000007</v>
+      </c>
+      <c r="E2045" t="n">
+        <v>1.09730155565578</v>
+      </c>
+      <c r="G2045" t="n">
+        <v>26090</v>
+      </c>
+      <c r="H2045" t="n">
+        <v>26140</v>
+      </c>
+      <c r="K2045" t="n">
+        <v>26044</v>
+      </c>
+      <c r="L2045" t="n">
+        <v>26107</v>
+      </c>
+      <c r="M2045" t="n">
+        <v>25796</v>
       </c>
     </row>
   </sheetData>
@@ -42365,13 +42399,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25886</v>
+        <v>25884</v>
       </c>
       <c r="C69" t="n">
-        <v>26064</v>
+        <v>26066</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -42425,12 +42459,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,400</t>
+          <t>26,090</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,500</t>
+          <t>26,140</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42461,12 +42495,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,967</t>
+          <t>25,971</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,067</t>
+          <t>26,071</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42479,12 +42513,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,102</t>
+          <t>26,044</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,170</t>
+          <t>26,107</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42497,12 +42531,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,824</t>
+          <t>25,796</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,824</t>
+          <t>25,796</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2045</f>
+              <f>'Time Series'!$A$2:$A$2046</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2045</f>
+              <f>'Time Series'!$B$2:$B$2046</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2045</f>
+              <f>'Time Series'!$A$2:$A$2046</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2045</f>
+              <f>'Time Series'!$C$2:$C$2046</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2045</f>
+              <f>'Time Series'!$A$2:$A$2046</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2045</f>
+              <f>'Time Series'!$E$2:$E$2046</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-27 12:00</t>
+          <t>Last Updated: 2026-10-28 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,832</t>
+          <t>25,806</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,115</t>
+          <t>26,055</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,044</t>
+          <t>26,134</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,107</t>
+          <t>26,162</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.12%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2045"/>
+  <dimension ref="A1:O2046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41622,6 +41622,40 @@
       </c>
       <c r="M2045" t="n">
         <v>25796</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2046" t="n">
+        <v>25805.82</v>
+      </c>
+      <c r="C2046" t="n">
+        <v>26055</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>249.1800000000003</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>0.9655961329653554</v>
+      </c>
+      <c r="G2046" t="n">
+        <v>26030</v>
+      </c>
+      <c r="H2046" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2046" t="n">
+        <v>26134</v>
+      </c>
+      <c r="L2046" t="n">
+        <v>26162</v>
+      </c>
+      <c r="M2046" t="n">
+        <v>25822</v>
       </c>
     </row>
   </sheetData>
@@ -42399,13 +42433,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25884</v>
+        <v>25881</v>
       </c>
       <c r="C69" t="n">
         <v>26066</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -42459,12 +42493,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,090</t>
+          <t>26,030</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,140</t>
+          <t>26,080</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42495,12 +42529,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,971</t>
+          <t>25,993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,071</t>
+          <t>26,093</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42513,12 +42547,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,044</t>
+          <t>26,134</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,107</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42531,12 +42565,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,796</t>
+          <t>25,822</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,796</t>
+          <t>25,822</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2046</f>
+              <f>'Time Series'!$A$2:$A$2047</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2046</f>
+              <f>'Time Series'!$B$2:$B$2047</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2046</f>
+              <f>'Time Series'!$A$2:$A$2047</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2046</f>
+              <f>'Time Series'!$C$2:$C$2047</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2046</f>
+              <f>'Time Series'!$A$2:$A$2047</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2046</f>
+              <f>'Time Series'!$E$2:$E$2047</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-28 12:00</t>
+          <t>Last Updated: 2026-10-29 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,806</t>
+          <t>25,834</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,134</t>
+          <t>26,109</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>26,126</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2046"/>
+  <dimension ref="A1:O2047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41656,6 +41656,40 @@
       </c>
       <c r="M2046" t="n">
         <v>25822</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2047" t="n">
+        <v>25834.04</v>
+      </c>
+      <c r="C2047" t="n">
+        <v>26055</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>220.9599999999991</v>
+      </c>
+      <c r="E2047" t="n">
+        <v>0.8553056355103542</v>
+      </c>
+      <c r="G2047" t="n">
+        <v>26030</v>
+      </c>
+      <c r="H2047" t="n">
+        <v>26080</v>
+      </c>
+      <c r="K2047" t="n">
+        <v>26109</v>
+      </c>
+      <c r="L2047" t="n">
+        <v>26126</v>
+      </c>
+      <c r="M2047" t="n">
+        <v>25797</v>
       </c>
     </row>
   </sheetData>
@@ -42433,13 +42467,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25881</v>
+        <v>25880</v>
       </c>
       <c r="C69" t="n">
         <v>26066</v>
       </c>
       <c r="D69" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -42529,12 +42563,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,993</t>
+          <t>25,985</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,093</t>
+          <t>26,085</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42547,12 +42581,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,134</t>
+          <t>26,109</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>26,126</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42565,12 +42599,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,797</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,797</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2047</f>
+              <f>'Time Series'!$A$2:$A$2048</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2047</f>
+              <f>'Time Series'!$B$2:$B$2048</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2047</f>
+              <f>'Time Series'!$A$2:$A$2048</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2047</f>
+              <f>'Time Series'!$C$2:$C$2048</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2047</f>
+              <f>'Time Series'!$A$2:$A$2048</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2047</f>
+              <f>'Time Series'!$E$2:$E$2048</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-29 12:00</t>
+          <t>Last Updated: 2026-10-30 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,834</t>
+          <t>25,792</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,055</t>
+          <t>26,175</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,109</t>
+          <t>25,892</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,126</t>
+          <t>25,822</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2047"/>
+  <dimension ref="A1:O2048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41690,6 +41690,40 @@
       </c>
       <c r="M2047" t="n">
         <v>25797</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2048" t="n">
+        <v>25792.39</v>
+      </c>
+      <c r="C2048" t="n">
+        <v>26175</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>382.6100000000006</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>1.483422048131253</v>
+      </c>
+      <c r="G2048" t="n">
+        <v>26140</v>
+      </c>
+      <c r="H2048" t="n">
+        <v>26210</v>
+      </c>
+      <c r="K2048" t="n">
+        <v>25892</v>
+      </c>
+      <c r="L2048" t="n">
+        <v>25822</v>
+      </c>
+      <c r="M2048" t="n">
+        <v>25782</v>
       </c>
     </row>
   </sheetData>
@@ -42467,13 +42501,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25880</v>
+        <v>25877</v>
       </c>
       <c r="C69" t="n">
-        <v>26066</v>
+        <v>26069</v>
       </c>
       <c r="D69" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -42527,12 +42561,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,030</t>
+          <t>26,140</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,080</t>
+          <t>26,210</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42563,12 +42597,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,985</t>
+          <t>26,029</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26,085</t>
+          <t>26,129</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -42581,12 +42615,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,109</t>
+          <t>25,892</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26,126</t>
+          <t>25,822</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42599,12 +42633,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,797</t>
+          <t>25,782</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,797</t>
+          <t>25,782</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>

--- a/analysis/USDVND_Analysis.xlsx
+++ b/analysis/USDVND_Analysis.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2048</f>
+              <f>'Time Series'!$A$2:$A$2049</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$B$2:$B$2048</f>
+              <f>'Time Series'!$B$2:$B$2049</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2048</f>
+              <f>'Time Series'!$A$2:$A$2049</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$C$2:$C$2048</f>
+              <f>'Time Series'!$C$2:$C$2049</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Time Series'!$A$2:$A$2048</f>
+              <f>'Time Series'!$A$2:$A$2049</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Time Series'!$E$2:$E$2048</f>
+              <f>'Time Series'!$E$2:$E$2049</f>
             </numRef>
           </val>
         </ser>
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated: 2026-10-30 12:00</t>
+          <t>Last Updated: 2026-10-31 12:00</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,792</t>
+          <t>25,802</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,175</t>
+          <t>25,740</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>-0.24%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,892</t>
+          <t>25,751</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,817</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>-0.24%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.11%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2048"/>
+  <dimension ref="A1:O2049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41724,6 +41724,40 @@
       </c>
       <c r="M2048" t="n">
         <v>25782</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B2049" t="n">
+        <v>25802.15</v>
+      </c>
+      <c r="C2049" t="n">
+        <v>25740</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>-62.15000000000146</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>-0.2408714002515351</v>
+      </c>
+      <c r="G2049" t="n">
+        <v>25700</v>
+      </c>
+      <c r="H2049" t="n">
+        <v>25780</v>
+      </c>
+      <c r="K2049" t="n">
+        <v>25751</v>
+      </c>
+      <c r="L2049" t="n">
+        <v>25817</v>
+      </c>
+      <c r="M2049" t="n">
+        <v>25784</v>
       </c>
     </row>
   </sheetData>
@@ -42501,13 +42535,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25877</v>
+        <v>25874</v>
       </c>
       <c r="C69" t="n">
-        <v>26069</v>
+        <v>26059</v>
       </c>
       <c r="D69" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -42561,12 +42595,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,140</t>
+          <t>25,700</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26,210</t>
+          <t>25,780</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -42615,12 +42649,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,892</t>
+          <t>25,751</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25,822</t>
+          <t>25,817</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -42633,12 +42667,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,782</t>
+          <t>25,784</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25,782</t>
+          <t>25,784</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
